--- a/FPO_Dashboard.xlsx
+++ b/FPO_Dashboard.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPO_Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{231F7ECF-21AB-4C00-84D3-7323DD7284A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C12113-5565-4013-8096-DBF7029D4A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{08C0F3C2-BCA0-4DE6-8CAC-810E617DC01B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{08C0F3C2-BCA0-4DE6-8CAC-810E617DC01B}"/>
   </bookViews>
   <sheets>
     <sheet name="Mature" sheetId="1" r:id="rId1"/>
-    <sheet name="Rules" sheetId="5" r:id="rId2"/>
-    <sheet name="Response" sheetId="2" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId4"/>
+    <sheet name="Response" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
+    <sheet name="Rules" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="341">
   <si>
     <t>Components</t>
   </si>
@@ -963,36 +963,103 @@
     <t>19.2.26</t>
   </si>
   <si>
-    <t>&lt;50%</t>
-  </si>
-  <si>
-    <t>&gt;50%</t>
-  </si>
-  <si>
-    <t>Percentage</t>
-  </si>
-  <si>
-    <t>Area of Improvements</t>
-  </si>
-  <si>
     <t>Action Plan</t>
   </si>
   <si>
-    <t>Proper management-reg related documents, staff and BoD awareness on reg docs and interpretation-use ofrelevant information contained in them</t>
-  </si>
-  <si>
-    <t>1. Training on FPO purpose and role, governance systems to FPO staff, leadership
-2. Proper filing and display of registration certificate, By-laws, MoA-AoA (facilitated by Resource Person)
-3. Filing returns for FPO with concerned agency for last FY after completion of necessary documentation (facilitated by Resource person)</t>
-  </si>
-  <si>
-    <t>Board orientation to FPO governance norms, their rights, duties, R&amp;R; improving financial management systems and tranparency through regular info sharing, institutional strengh, farmer mobilization at field level, member education, mandatory institutional and legal compliance-AGM, Annual Report; system for distribution</t>
-  </si>
-  <si>
-    <t>1. Training to FPO BoD on their roles, responsibilities, rights and duties
-2. Streamlining member education of FPOs (facilitated by
-Resource Person)
-3. Training on FPO Activity calendar, scope of each activity and key concepts in cooperative management to FPO staff and leadership</t>
+    <t>Registration</t>
+  </si>
+  <si>
+    <t>&lt;50</t>
+  </si>
+  <si>
+    <t>&gt;50</t>
+  </si>
+  <si>
+    <t>&gt;80</t>
+  </si>
+  <si>
+    <t>basic compliance gaps in registration</t>
+  </si>
+  <si>
+    <t>ensure registration, filings, and documentation are complete</t>
+  </si>
+  <si>
+    <t>partial compliance in registration</t>
+  </si>
+  <si>
+    <t>improve regular filings and documentation practices</t>
+  </si>
+  <si>
+    <t>minor gaps in compliance</t>
+  </si>
+  <si>
+    <t>strengthen monitoring and maintain records properly</t>
+  </si>
+  <si>
+    <t>fully compliant</t>
+  </si>
+  <si>
+    <t>continue best practices and periodic review</t>
+  </si>
+  <si>
+    <t>weak membership systems and records</t>
+  </si>
+  <si>
+    <t>establish proper membership processes and documentation</t>
+  </si>
+  <si>
+    <t>partial membership management</t>
+  </si>
+  <si>
+    <t>improve data tracking and member engagement</t>
+  </si>
+  <si>
+    <t>minor issues in membership handling</t>
+  </si>
+  <si>
+    <t>optimize member services and strengthen participation</t>
+  </si>
+  <si>
+    <t>strong membership system</t>
+  </si>
+  <si>
+    <t>maintain engagement and update records regularly</t>
+  </si>
+  <si>
+    <t>weak governance and institutional systems</t>
+  </si>
+  <si>
+    <t>build governance structure and conduct regular meetings</t>
+  </si>
+  <si>
+    <t>moderate governance practices</t>
+  </si>
+  <si>
+    <t>improve meeting documentation and financial updates</t>
+  </si>
+  <si>
+    <t>minor governance gaps</t>
+  </si>
+  <si>
+    <t>strengthen leadership and capacity building</t>
+  </si>
+  <si>
+    <t>strong governance system</t>
+  </si>
+  <si>
+    <t>sustain leadership practices and continuous improvement</t>
+  </si>
+  <si>
+    <t>Areas of Improvements</t>
+  </si>
+  <si>
+    <t>Section</t>
+  </si>
+  <si>
+    <t>Condition</t>
+  </si>
+  <si>
+    <t>Institutional Strength and Governance</t>
   </si>
 </sst>
 </file>
@@ -1002,7 +1069,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1106,8 +1173,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1124,6 +1196,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FFBDD6EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1222,7 +1300,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1329,11 +1407,31 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1648,7 +1746,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77B90A15-4161-42D3-B3CE-9840546853B1}">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="61.26953125" bestFit="1" customWidth="1"/>
@@ -1664,56 +1762,54 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="B2" s="29"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="39" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="31" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="30" t="s">
+      <c r="B3" s="38" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="39" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="31" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="30" t="s">
+      <c r="B4" s="38" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B5" s="38" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="30" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="B5" s="31" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="30" t="s">
+      <c r="B6" s="38" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="B6" s="31" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="38" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="30" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B8" s="31" t="s">
         <v>93</v>
@@ -1721,37 +1817,37 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="30" t="s">
         <v>132</v>
       </c>
-      <c r="B9" s="31" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="32" t="s">
+      <c r="B10" s="31" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="B10" s="31" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="33"/>
       <c r="B11" s="31" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="30" t="s">
-        <v>134</v>
-      </c>
+      <c r="A12" s="33"/>
       <c r="B12" s="31" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="30" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B13" s="31" t="s">
         <v>93</v>
@@ -1759,7 +1855,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="30" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="B14" s="31" t="s">
         <v>93</v>
@@ -1767,7 +1863,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="30" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B15" s="31" t="s">
         <v>93</v>
@@ -1775,7 +1871,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>93</v>
@@ -1783,7 +1879,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="30" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B17" s="31" t="s">
         <v>93</v>
@@ -1791,7 +1887,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="30" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B18" s="31" t="s">
         <v>93</v>
@@ -1799,7 +1895,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="30" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>93</v>
@@ -1807,7 +1903,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="30" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>93</v>
@@ -1815,7 +1911,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="30" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B21" s="31" t="s">
         <v>93</v>
@@ -1823,7 +1919,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B22" s="31" t="s">
         <v>93</v>
@@ -1831,7 +1927,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B23" s="31" t="s">
         <v>93</v>
@@ -1839,7 +1935,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B24" s="31" t="s">
         <v>93</v>
@@ -1847,23 +1943,23 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="B25" s="31" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="30" t="s">
         <v>169</v>
       </c>
-      <c r="B25" s="31" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A26" s="30" t="s">
+      <c r="B26" s="31" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A27" s="30" t="s">
         <v>171</v>
-      </c>
-      <c r="B26" s="31" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" s="30" t="s">
-        <v>173</v>
       </c>
       <c r="B27" s="31" t="s">
         <v>93</v>
@@ -1871,7 +1967,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="30" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B28" s="31" t="s">
         <v>93</v>
@@ -1879,69 +1975,29 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="B29" s="31" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="B29" s="31" t="s">
+      <c r="B30" s="31" t="s">
         <v>93</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A11:A12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4530720F-5FED-4616-96FF-2BB541E80620}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.08984375" customWidth="1"/>
-    <col min="3" max="3" width="46" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="38" t="s">
-        <v>310</v>
-      </c>
-      <c r="B1" s="38" t="s">
-        <v>311</v>
-      </c>
-      <c r="C1" s="38" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="39" t="s">
-        <v>309</v>
-      </c>
-      <c r="B2" s="40" t="s">
-        <v>313</v>
-      </c>
-      <c r="C2" s="40" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="39" t="s">
-        <v>308</v>
-      </c>
-      <c r="B3" s="40" t="s">
-        <v>315</v>
-      </c>
-      <c r="C3" s="40" t="s">
-        <v>316</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD10CCB5-CC50-489C-9092-7F34AC94A516}">
   <dimension ref="A1:ES3"/>
   <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3163,7 +3219,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85011925-41A6-47ED-B5ED-1C9B8D16FD6B}">
   <dimension ref="A1:C143"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4624,4 +4680,205 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4530720F-5FED-4616-96FF-2BB541E80620}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="28.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="28.08984375" style="44"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="40" t="s">
+        <v>338</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="D1" s="40" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>310</v>
+      </c>
+      <c r="C2" s="41" t="s">
+        <v>313</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>311</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>315</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>312</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>317</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="43">
+        <f>100</f>
+        <v>100</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>319</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="43" t="s">
+        <v>310</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>321</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>311</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>323</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="43" t="s">
+        <v>312</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>325</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="43">
+        <f>100</f>
+        <v>100</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>327</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="45" t="s">
+        <v>340</v>
+      </c>
+      <c r="B10" s="43" t="s">
+        <v>310</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>329</v>
+      </c>
+      <c r="D10" s="41" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="45" t="s">
+        <v>340</v>
+      </c>
+      <c r="B11" s="43" t="s">
+        <v>311</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>331</v>
+      </c>
+      <c r="D11" s="41" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A12" s="45" t="s">
+        <v>340</v>
+      </c>
+      <c r="B12" s="43" t="s">
+        <v>312</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>333</v>
+      </c>
+      <c r="D12" s="41" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A13" s="45" t="s">
+        <v>340</v>
+      </c>
+      <c r="B13" s="43">
+        <f>100</f>
+        <v>100</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>335</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="46"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>